--- a/public/assets/ICF Workshop.xlsx
+++ b/public/assets/ICF Workshop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03B451D-E6BB-4F3E-80F1-10A2020FFF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE034F9F-F967-401E-BD16-58A7C3218113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="229">
   <si>
     <t>Timestamp</t>
   </si>
@@ -631,6 +631,87 @@
   </si>
   <si>
     <t>drrohit47@gmail.com</t>
+  </si>
+  <si>
+    <t>mr.rajat08@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Rajat Mujalda</t>
+  </si>
+  <si>
+    <t>Dermatology Venereology and Leprosy</t>
+  </si>
+  <si>
+    <t>madhulikayadav07@gmail.com</t>
+  </si>
+  <si>
+    <t>Madhulika yadav</t>
+  </si>
+  <si>
+    <t>Resident</t>
+  </si>
+  <si>
+    <t>Ent</t>
+  </si>
+  <si>
+    <t>themohit008@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Rohit Choudhary</t>
+  </si>
+  <si>
+    <t>PG JR1</t>
+  </si>
+  <si>
+    <t>mksshaikh91@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Shaikh M Khaliq</t>
+  </si>
+  <si>
+    <t>Professor and Head of Biochemistry</t>
+  </si>
+  <si>
+    <t>Clinical Biochemistry</t>
+  </si>
+  <si>
+    <t>yogeshvalimbe92@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Yogesh Valimbe</t>
+  </si>
+  <si>
+    <t>Orthopedic Surgeon</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>khanharoon776.hk@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Haroon khan</t>
+  </si>
+  <si>
+    <t>PG1</t>
+  </si>
+  <si>
+    <t>jahanvisingh2312@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Jahanvi Singh</t>
+  </si>
+  <si>
+    <t>ruqqaiyabee786@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Ruqqaiya Bee</t>
+  </si>
+  <si>
+    <t>Scientific officer</t>
+  </si>
+  <si>
+    <t>Department of pathology (Central Research Lab)</t>
   </si>
 </sst>
 </file>
@@ -682,7 +763,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -812,10 +893,70 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF442F65"/>
       </left>
       <right style="medium">
         <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
@@ -830,10 +971,40 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
         <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -848,7 +1019,7 @@
         <color rgb="FF442F65"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -859,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -894,16 +1065,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1186,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1225,28 +1420,28 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="12">
         <v>46252.694108796299</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="14">
         <v>9300409555</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2733,28 +2928,236 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="12">
+      <c r="A60" s="4">
         <v>46263.593414351853</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="6">
         <v>9109110092</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="G60" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="H60" s="15" t="s">
+      <c r="H60" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>46263.749513888892</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F61" s="10">
+        <v>9407133385</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>46265.339282407411</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" s="6">
+        <v>7771075573</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>46265.34171296296</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F63" s="10">
+        <v>8441905981</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>46265.612719907411</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F64" s="6">
+        <v>9826647786</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>46266.355821759258</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F65" s="10">
+        <v>9425049415</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
+        <v>46266.376076388886</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F66" s="6">
+        <v>7742627345</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="16">
+        <v>46266.376111111109</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="18">
+        <v>7266935975</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="20">
+        <v>46266.515208333331</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F68" s="22">
+        <v>7024471185</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H68" s="23" t="s">
         <v>17</v>
       </c>
     </row>
